--- a/mica/NFDI4Health.KARMEN_P2.R-dictionary.xlsx
+++ b/mica/NFDI4Health.KARMEN_P2.R-dictionary.xlsx
@@ -7999,7 +7999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8010,35 +8010,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Project1</t>
+          <t>index</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>valueType</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>valueType</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -8050,28 +8045,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Participant identification number</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Participant identification number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8083,28 +8075,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C3">
+      <c r="B3">
         <v>2</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8116,28 +8105,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4">
+      <c r="B4">
         <v>3</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGE_BASE</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGE_BASE</t>
+          <t>Age at exposure measure [years]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Age at exposure measure [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8149,28 +8135,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B5" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5">
+      <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDU_LEVEL</t>
+          <t>Highest level of education [ISCED 2011]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Highest level of education [ISCED 2011]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8182,28 +8165,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6">
+      <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMPLOY</t>
+          <t>Employment</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Employment</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8215,28 +8195,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7">
+      <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IMMIGRATION</t>
+          <t>Immigration background</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Immigration background</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8248,28 +8225,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B8" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8">
+      <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TOT_PA_QX</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TOT_PA_QX</t>
+          <t>Physical activity from questionnaire data [MET-hr/day]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Physical activity from questionnaire data [MET-hr/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8281,28 +8255,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9">
+      <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TOT_PA_AC</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TOT_PA_AC</t>
+          <t>Physical activity from accelerometry data [MET-hr/day]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Physical activity from accelerometry data [MET-hr/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8314,28 +8285,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10">
+      <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SMOKE_ST</t>
+          <t>Smoking status</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smoking status</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8347,28 +8315,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B11" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11">
+      <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOBACCO_PY</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TOBACCO_PY</t>
+          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8380,28 +8345,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12">
+      <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOBACCO_D</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TOBACCO_D</t>
+          <t>Amount of daily tobacco smoked [g/day]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amount of daily tobacco smoked [g/day]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8413,28 +8375,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B13" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13">
+      <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AGE_SMOKE_QUIT</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGE_SMOKE_QUIT</t>
+          <t>Age at time of quitting smoking [years]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Age at time of quitting smoking [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8446,28 +8405,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14">
+      <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MED_SUPPL</t>
+          <t>Regular use of  vitamin/multivitamin supplements</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Regular use of  vitamin/multivitamin supplements</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8479,28 +8435,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15">
+      <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MENOPAUSE</t>
+          <t>Menopause status</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Menopause status</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8512,28 +8465,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B16" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16">
+      <c r="B16">
         <v>15</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HRT</t>
+          <t>Hormone replacement therapy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hormone replacement therapy</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8545,28 +8495,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B17" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17">
+      <c r="B17">
         <v>16</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CONTRACEPTIVE</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CONTRACEPTIVE</t>
+          <t>Use of contraceptive pills or injections [years]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Use of contraceptive pills or injections [years]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8578,28 +8525,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18">
+      <c r="B18">
         <v>17</v>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIVE_BIRTHS</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LIVE_BIRTHS</t>
+          <t>Number of live births given [Nr. of birth]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Number of live births given [Nr. of birth]</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8611,28 +8555,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B19" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19">
+      <c r="B19">
         <v>18</v>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AGE_FIRST_BIRTH</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AGE_FIRST_BIRTH</t>
+          <t>Age at the first given birth [years]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Age at the first given birth [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8644,28 +8585,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B20" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20">
+      <c r="B20">
         <v>19</v>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>Triglycerides measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Triglycerides measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8677,28 +8615,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B21" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21">
+      <c r="B21">
         <v>20</v>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHOL</t>
+          <t>Total cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Total cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8710,28 +8645,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B22" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22">
+      <c r="B22">
         <v>21</v>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LDL</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LDL</t>
+          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8743,28 +8675,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B23" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23">
+      <c r="B23">
         <v>22</v>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HDL</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HDL</t>
+          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8776,28 +8705,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B24" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24">
+      <c r="B24">
         <v>23</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PREV_DIAB</t>
+          <t>History of diabetes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>History of diabetes</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8809,28 +8735,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B25" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25">
+      <c r="B25">
         <v>24</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PREV_HYP</t>
+          <t>History of hypertension</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>History of hypertension</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8842,28 +8765,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B26" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26">
+      <c r="B26">
         <v>25</v>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PREV_CVD</t>
+          <t>History of cardiovascular disease</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>History of cardiovascular disease</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8875,28 +8795,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B27" t="b">
-        <v>0</v>
-      </c>
-      <c r="C27">
+      <c r="B27">
         <v>26</v>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PREV_CANCER</t>
+          <t>History of cancer</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>History of cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8908,28 +8825,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B28" t="b">
-        <v>0</v>
-      </c>
-      <c r="C28">
+      <c r="B28">
         <v>27</v>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FAM1_CHD_STROKE</t>
+          <t>First degree family history of premature CHD and stroke</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>First degree family history of premature CHD and stroke</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8941,28 +8855,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B29" t="b">
-        <v>0</v>
-      </c>
-      <c r="C29">
+      <c r="B29">
         <v>28</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FAM1_DIAB2</t>
+          <t>First degree family history of T2D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>First degree family history of T2D</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8974,28 +8885,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B30" t="b">
-        <v>0</v>
-      </c>
-      <c r="C30">
+      <c r="B30">
         <v>29</v>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FAM1_CANCER</t>
+          <t>First degree family history of cancer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>First degree family history of cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9007,28 +8915,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B31" t="b">
-        <v>0</v>
-      </c>
-      <c r="C31">
+      <c r="B31">
         <v>30</v>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DRE_SCREEN</t>
+          <t>Screening, DRE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Screening, DRE</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9040,28 +8945,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B32" t="b">
-        <v>0</v>
-      </c>
-      <c r="C32">
+      <c r="B32">
         <v>31</v>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PSA_SCREEN</t>
+          <t>Screening, PSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Screening, PSA</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9073,28 +8975,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B33" t="b">
-        <v>0</v>
-      </c>
-      <c r="C33">
+      <c r="B33">
         <v>32</v>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FOBT_SCREEN</t>
+          <t>Screening, FOBT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Screening, FOBT</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9106,28 +9005,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B34" t="b">
-        <v>0</v>
-      </c>
-      <c r="C34">
+      <c r="B34">
         <v>33</v>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>COL_SCREEN</t>
+          <t>Screening, colonoscopy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Screening, colonoscopy</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9139,28 +9035,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B35" t="b">
-        <v>0</v>
-      </c>
-      <c r="C35">
+      <c r="B35">
         <v>34</v>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MELANOMA_SCREEN</t>
+          <t>Screening, skin cancer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Screening, skin cancer</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9172,28 +9065,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B36" t="b">
-        <v>0</v>
-      </c>
-      <c r="C36">
+      <c r="B36">
         <v>35</v>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MAMMO_SCREEN</t>
+          <t>Screening, mammography</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Screening, mammography</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9205,28 +9095,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B37" t="b">
-        <v>0</v>
-      </c>
-      <c r="C37">
+      <c r="B37">
         <v>36</v>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CERVICAL_SCREEN</t>
+          <t>Screening cervical, smear test</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Screening cervical, smear test</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9238,28 +9125,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B38" t="b">
-        <v>0</v>
-      </c>
-      <c r="C38">
+      <c r="B38">
         <v>37</v>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MED_STAT</t>
+          <t>Regular use of statins</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Regular use of statins</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9271,28 +9155,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B39" t="b">
-        <v>0</v>
-      </c>
-      <c r="C39">
+      <c r="B39">
         <v>38</v>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MED_NSAID</t>
+          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9304,28 +9185,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B40" t="b">
-        <v>0</v>
-      </c>
-      <c r="C40">
+      <c r="B40">
         <v>39</v>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>INC_CVD</t>
+          <t>CVD event during follow-up</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CVD event during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9337,28 +9215,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B41" t="b">
-        <v>0</v>
-      </c>
-      <c r="C41">
+      <c r="B41">
         <v>40</v>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AGE_CVD</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AGE_CVD</t>
+          <t>Age at diagnosis of CVD [years]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Age at diagnosis of CVD [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9370,28 +9245,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B42" t="b">
-        <v>0</v>
-      </c>
-      <c r="C42">
+      <c r="B42">
         <v>41</v>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INC_ANGINA</t>
+          <t>Angina pectoris event during follow-up</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Angina pectoris event during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9403,28 +9275,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B43" t="b">
-        <v>0</v>
-      </c>
-      <c r="C43">
+      <c r="B43">
         <v>42</v>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AGE_ANGINA</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AGE_ANGINA</t>
+          <t>Age at diagnosis of angina pectoris [years]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Age at diagnosis of angina pectoris [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9436,28 +9305,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C44">
+      <c r="B44">
         <v>43</v>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INC_MI</t>
+          <t>Myocardial infarction during follow-up</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Myocardial infarction during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9469,28 +9335,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B45" t="b">
-        <v>0</v>
-      </c>
-      <c r="C45">
+      <c r="B45">
         <v>44</v>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AGE_MI</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AGE_MI</t>
+          <t>Age at diagnosis of myocardial infarction [years]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Age at diagnosis of myocardial infarction [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9502,28 +9365,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B46" t="b">
-        <v>0</v>
-      </c>
-      <c r="C46">
+      <c r="B46">
         <v>45</v>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INC_STR</t>
+          <t>Stroke during follow-up</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stroke during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9535,28 +9395,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B47" t="b">
-        <v>0</v>
-      </c>
-      <c r="C47">
+      <c r="B47">
         <v>46</v>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AGE_STR</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AGE_STR</t>
+          <t>Age at diagnosis of stroke [years]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Age at diagnosis of stroke [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9568,28 +9425,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B48" t="b">
-        <v>0</v>
-      </c>
-      <c r="C48">
+      <c r="B48">
         <v>47</v>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INC_ISC_STR</t>
+          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9601,28 +9455,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C49">
+      <c r="B49">
         <v>48</v>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AGE_ISC_STR</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AGE_ISC_STR</t>
+          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9634,28 +9485,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B50" t="b">
-        <v>0</v>
-      </c>
-      <c r="C50">
+      <c r="B50">
         <v>49</v>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INC_HAEMO_STR</t>
+          <t>Haemorrhagic stroke during follow-up</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Haemorrhagic stroke during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9667,28 +9515,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B51" t="b">
-        <v>0</v>
-      </c>
-      <c r="C51">
+      <c r="B51">
         <v>50</v>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AGE_HAEMO_STR</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AGE_HAEMO_STR</t>
+          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9700,28 +9545,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B52" t="b">
-        <v>0</v>
-      </c>
-      <c r="C52">
+      <c r="B52">
         <v>51</v>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INC_HYP</t>
+          <t>Essential hypertension during follow-up</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Essential hypertension during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9733,28 +9575,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B53" t="b">
-        <v>0</v>
-      </c>
-      <c r="C53">
+      <c r="B53">
         <v>52</v>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AGE_HYP</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AGE_HYP</t>
+          <t>Age at diagnosis of essential hypertension [years]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Age at diagnosis of essential hypertension [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9766,28 +9605,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B54" t="b">
-        <v>0</v>
-      </c>
-      <c r="C54">
+      <c r="B54">
         <v>53</v>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INC_HF</t>
+          <t>Heart failure during follow-up</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heart failure during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9799,28 +9635,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B55" t="b">
-        <v>0</v>
-      </c>
-      <c r="C55">
+      <c r="B55">
         <v>54</v>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AGE_HF</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AGE_HF</t>
+          <t>Age at diagnosis of heart failure [years]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Age at diagnosis of heart failure [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9832,28 +9665,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B56" t="b">
-        <v>0</v>
-      </c>
-      <c r="C56">
+      <c r="B56">
         <v>55</v>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INC_DIAB2</t>
+          <t>Diabetes mellitus type 2 during follow-up</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Diabetes mellitus type 2 during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9865,28 +9695,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B57" t="b">
-        <v>0</v>
-      </c>
-      <c r="C57">
+      <c r="B57">
         <v>56</v>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AGE_DIAB2</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AGE_DIAB2</t>
+          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9898,28 +9725,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B58" t="b">
-        <v>0</v>
-      </c>
-      <c r="C58">
+      <c r="B58">
         <v>57</v>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INC_CANCER</t>
+          <t>Cancer during follow-up</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cancer during follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9931,28 +9755,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B59" t="b">
-        <v>0</v>
-      </c>
-      <c r="C59">
+      <c r="B59">
         <v>58</v>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TYPE_CANCER</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TYPE_CANCER</t>
+          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9964,28 +9785,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B60" t="b">
-        <v>0</v>
-      </c>
-      <c r="C60">
+      <c r="B60">
         <v>59</v>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AGE_CANCER</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AGE_CANCER</t>
+          <t>Age at diagnosis of cancer [years]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Age at diagnosis of cancer [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9997,28 +9815,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B61" t="b">
-        <v>0</v>
-      </c>
-      <c r="C61">
+      <c r="B61">
         <v>60</v>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VITAL_ST</t>
+          <t>Vital status at the end of mortality follow-up</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vital status at the end of mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10030,28 +9845,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B62" t="b">
-        <v>0</v>
-      </c>
-      <c r="C62">
+      <c r="B62">
         <v>61</v>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AGE_DEATH</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AGE_DEATH</t>
+          <t>Age at time of death [years]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Age at time of death [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10063,28 +9875,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B63" t="b">
-        <v>0</v>
-      </c>
-      <c r="C63">
+      <c r="B63">
         <v>62</v>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VITAL_ST_CVD</t>
+          <t>Vital status at the end of CVD mortality follow-up</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vital status at the end of CVD mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10096,28 +9905,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B64" t="b">
-        <v>0</v>
-      </c>
-      <c r="C64">
+      <c r="B64">
         <v>63</v>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VITAL_ST_CANCER</t>
+          <t>Vital status at the end of cancer mortality follow-up</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vital status at the end of cancer mortality follow-up</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10129,28 +9935,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B65" t="b">
-        <v>0</v>
-      </c>
-      <c r="C65">
+      <c r="B65">
         <v>64</v>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AGE_FUP</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AGE_FUP</t>
+          <t>Age at end of follow-up [years]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Age at end of follow-up [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10162,28 +9965,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B66" t="b">
-        <v>0</v>
-      </c>
-      <c r="C66">
+      <c r="B66">
         <v>65</v>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BMI</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>Body Mass Index at baseline [kg/m²]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Body Mass Index at baseline [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10195,28 +9995,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B67" t="b">
-        <v>0</v>
-      </c>
-      <c r="C67">
+      <c r="B67">
         <v>66</v>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BMI_FUP</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BMI_FUP</t>
+          <t>Body Mass Index at follow-up [kg/m²]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Body Mass Index at follow-up [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10228,28 +10025,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B68" t="b">
-        <v>0</v>
-      </c>
-      <c r="C68">
+      <c r="B68">
         <v>67</v>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BMI_SDS</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BMI_SDS</t>
+          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10261,28 +10055,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B69" t="b">
-        <v>0</v>
-      </c>
-      <c r="C69">
+      <c r="B69">
         <v>68</v>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BMI_SDS_FUP</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BMI_SDS_FUP</t>
+          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10294,28 +10085,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B70" t="b">
-        <v>0</v>
-      </c>
-      <c r="C70">
+      <c r="B70">
         <v>69</v>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>WAIST_FUP</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>WAIST_FUP</t>
+          <t>Waist circumference at follow-up [cm]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Waist circumference at follow-up [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10327,28 +10115,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B71" t="b">
-        <v>0</v>
-      </c>
-      <c r="C71">
+      <c r="B71">
         <v>70</v>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>WAIST</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>WAIST</t>
+          <t>Waist circumference at baseline [cm]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Waist circumference at baseline [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10360,28 +10145,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B72" t="b">
-        <v>0</v>
-      </c>
-      <c r="C72">
+      <c r="B72">
         <v>71</v>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HIP</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HIP</t>
+          <t>Hip circumference at baseline [cm]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hip circumference at baseline [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10393,28 +10175,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B73" t="b">
-        <v>0</v>
-      </c>
-      <c r="C73">
+      <c r="B73">
         <v>72</v>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HIP_FUP</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIP_FUP</t>
+          <t>Hip circumference at follow-up [cm]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hip circumference at follow-up [cm]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10426,28 +10205,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B74" t="b">
-        <v>0</v>
-      </c>
-      <c r="C74">
+      <c r="B74">
         <v>73</v>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FMI_FUP</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FMI_FUP</t>
+          <t>Fat mass index at follow-up  [kg/m²]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fat mass index at follow-up  [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10459,28 +10235,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B75" t="b">
-        <v>0</v>
-      </c>
-      <c r="C75">
+      <c r="B75">
         <v>74</v>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FMI</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FMI</t>
+          <t>Fat mass index at baseline  [kg/m²]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fat mass index at baseline  [kg/m²]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10492,28 +10265,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B76" t="b">
-        <v>0</v>
-      </c>
-      <c r="C76">
+      <c r="B76">
         <v>75</v>
       </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BODY_FAT_FUP</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BODY_FAT_FUP</t>
+          <t>Body fat precent at follow-up [%]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Body fat precent at follow-up [%]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10525,28 +10295,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B77" t="b">
-        <v>0</v>
-      </c>
-      <c r="C77">
+      <c r="B77">
         <v>76</v>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BODY_FAT</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BODY_FAT</t>
+          <t>Body fat precent at baseline  [%]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Body fat precent at baseline  [%]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10558,28 +10325,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B78" t="b">
-        <v>0</v>
-      </c>
-      <c r="C78">
+      <c r="B78">
         <v>77</v>
       </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AGE_ANTH_FUP</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AGE_ANTH_FUP</t>
+          <t>Age at anthropometric measurement at follow-up [years]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Age at anthropometric measurement at follow-up [years]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10591,28 +10355,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B79" t="b">
-        <v>0</v>
-      </c>
-      <c r="C79">
+      <c r="B79">
         <v>78</v>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>Energy intake [kcal/d]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Energy intake [kcal/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10624,28 +10385,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B80" t="b">
-        <v>0</v>
-      </c>
-      <c r="C80">
+      <c r="B80">
         <v>79</v>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CARB</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CARB</t>
+          <t>Carbohydrate intake [g/d]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Carbohydrate intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10657,28 +10415,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B81" t="b">
-        <v>0</v>
-      </c>
-      <c r="C81">
+      <c r="B81">
         <v>80</v>
       </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PROT</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PROT</t>
+          <t>Protein intake [g/d]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Protein intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10690,28 +10445,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B82" t="b">
-        <v>0</v>
-      </c>
-      <c r="C82">
+      <c r="B82">
         <v>81</v>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FAT</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FAT</t>
+          <t>Fat intake [g/d]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10723,28 +10475,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B83" t="b">
-        <v>0</v>
-      </c>
-      <c r="C83">
+      <c r="B83">
         <v>82</v>
       </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ALC</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ALC</t>
+          <t>Alcohol intake [g/d]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcohol intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10756,28 +10505,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B84" t="b">
-        <v>0</v>
-      </c>
-      <c r="C84">
+      <c r="B84">
         <v>83</v>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FIBER</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FIBER</t>
+          <t>Dietary fiber intake [g/d]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dietary fiber intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10789,28 +10535,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B85" t="b">
-        <v>0</v>
-      </c>
-      <c r="C85">
+      <c r="B85">
         <v>84</v>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SFA</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SFA</t>
+          <t>Saturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10822,28 +10565,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B86" t="b">
-        <v>0</v>
-      </c>
-      <c r="C86">
+      <c r="B86">
         <v>85</v>
       </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MUFA</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MUFA</t>
+          <t>Monounsaturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Monounsaturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10855,28 +10595,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B87" t="b">
-        <v>0</v>
-      </c>
-      <c r="C87">
+      <c r="B87">
         <v>86</v>
       </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PUFA</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PUFA</t>
+          <t>Polyunsaturated fat intake [g/d]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polyunsaturated fat intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10888,28 +10625,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B88" t="b">
-        <v>0</v>
-      </c>
-      <c r="C88">
+      <c r="B88">
         <v>87</v>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TOT_SUGARS</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TOT_SUGARS</t>
+          <t>Total sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Total sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10921,28 +10655,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B89" t="b">
-        <v>0</v>
-      </c>
-      <c r="C89">
+      <c r="B89">
         <v>88</v>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ADD_SUGARS</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ADD_SUGARS</t>
+          <t>Added sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Added sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10954,28 +10685,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B90" t="b">
-        <v>0</v>
-      </c>
-      <c r="C90">
+      <c r="B90">
         <v>89</v>
       </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FREE_SUGARS</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FREE_SUGARS</t>
+          <t>Free sugar intake [g/d]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Free sugar intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10987,28 +10715,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B91" t="b">
-        <v>0</v>
-      </c>
-      <c r="C91">
+      <c r="B91">
         <v>90</v>
       </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GLUC</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GLUC</t>
+          <t>Glucose intake [g/d]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Glucose intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11020,28 +10745,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B92" t="b">
-        <v>0</v>
-      </c>
-      <c r="C92">
+      <c r="B92">
         <v>91</v>
       </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FRUC</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FRUC</t>
+          <t>Fructose intake [g/d]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fructose intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11053,28 +10775,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B93" t="b">
-        <v>0</v>
-      </c>
-      <c r="C93">
+      <c r="B93">
         <v>92</v>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GI</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>Daily glycaemic index</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Daily glycaemic index</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11086,28 +10805,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B94" t="b">
-        <v>0</v>
-      </c>
-      <c r="C94">
+      <c r="B94">
         <v>93</v>
       </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>Daily glycaemic load</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Daily glycaemic load</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11119,28 +10835,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B95" t="b">
-        <v>0</v>
-      </c>
-      <c r="C95">
+      <c r="B95">
         <v>94</v>
       </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SODIUM</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SODIUM</t>
+          <t>Sodium intake [mg/d]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sodium intake [mg/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11152,28 +10865,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B96" t="b">
-        <v>0</v>
-      </c>
-      <c r="C96">
+      <c r="B96">
         <v>95</v>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SOD_POT_RATIO</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SOD_POT_RATIO</t>
+          <t>Sodium to potassium intake ratio</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sodium to potassium intake ratio</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11185,28 +10895,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B97" t="b">
-        <v>0</v>
-      </c>
-      <c r="C97">
+      <c r="B97">
         <v>96</v>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SUGAR_CONFECT_11</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
+          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11218,28 +10925,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B98" t="b">
-        <v>0</v>
-      </c>
-      <c r="C98">
+      <c r="B98">
         <v>97</v>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CAKES_12</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
+          <t>Intake of cakes and fine bakery products [g/d]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11251,28 +10955,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B99" t="b">
-        <v>0</v>
-      </c>
-      <c r="C99">
+      <c r="B99">
         <v>98</v>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FRUITVEG_JUICE_1301</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
+          <t>Intake of fruit and vegetable juices [g/d]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11284,28 +10985,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B100" t="b">
-        <v>0</v>
-      </c>
-      <c r="C100">
+      <c r="B100">
         <v>99</v>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SOFTDRINKS_1302</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
+          <t>Intake of soft drinks [g/d]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Intake of soft drinks [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11317,28 +11015,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B101" t="b">
-        <v>0</v>
-      </c>
-      <c r="C101">
+      <c r="B101">
         <v>100</v>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ART_SWEETENER_170201</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ART_SWEETENER_170201</t>
+          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11350,28 +11045,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B102" t="b">
-        <v>0</v>
-      </c>
-      <c r="C102">
+      <c r="B102">
         <v>101</v>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>VEGETABLES_02</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VEGETABLES_02</t>
+          <t>Vegetable intake [g/d]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vegetable intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11383,28 +11075,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B103" t="b">
-        <v>0</v>
-      </c>
-      <c r="C103">
+      <c r="B103">
         <v>102</v>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LEGUMES_TOT_03</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LEGUMES_TOT_03</t>
+          <t>Total legumes intake [g/d]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Total legumes intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11416,28 +11105,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B104" t="b">
-        <v>0</v>
-      </c>
-      <c r="C104">
+      <c r="B104">
         <v>103</v>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FRUITS_TOT_04</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FRUITS_TOT_04</t>
+          <t>Total fruit intake [g/d]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Total fruit intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11449,28 +11135,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B105" t="b">
-        <v>0</v>
-      </c>
-      <c r="C105">
+      <c r="B105">
         <v>104</v>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RED_MEAT_0701</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RED_MEAT_0701</t>
+          <t>Intake of red meat (mammals meat) [g/d]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11482,28 +11165,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B106" t="b">
-        <v>0</v>
-      </c>
-      <c r="C106">
+      <c r="B106">
         <v>105</v>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PROCMEAT_0704</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PROCMEAT_0704</t>
+          <t>Intake of processed or preserved meat [g/d]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11515,28 +11195,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B107" t="b">
-        <v>0</v>
-      </c>
-      <c r="C107">
+      <c r="B107">
         <v>106</v>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>COFFEE_130301</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>COFFEE_130301</t>
+          <t>Coffee intake [g/d]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coffee intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11548,28 +11225,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B108" t="b">
-        <v>0</v>
-      </c>
-      <c r="C108">
+      <c r="B108">
         <v>107</v>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TEA_130302</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TEA_130302</t>
+          <t>Tea intake [g/d]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tea intake [g/d]</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11581,28 +11255,25 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B109" t="b">
-        <v>0</v>
-      </c>
-      <c r="C109">
+      <c r="B109">
         <v>108</v>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIETARY_ASSESS_INSTR</t>
+          <t>Dietary Assessment Instrument</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dietary Assessment Instrument</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/mica/NFDI4Health.KARMEN_P2.R-dictionary.xlsx
+++ b/mica/NFDI4Health.KARMEN_P2.R-dictionary.xlsx
@@ -7999,7 +7999,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8010,30 +8010,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>valueType</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
@@ -8045,25 +8040,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Participant identification number</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8075,25 +8065,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SEX</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8105,25 +8090,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AGE_BASE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Age at exposure measure [years]</t>
-        </is>
+          <t>Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8135,25 +8115,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B5">
-        <v>4</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EDU_LEVEL</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Highest level of education [ISCED 2011]</t>
-        </is>
+          <t>Primary Education</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8165,25 +8140,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B6">
-        <v>5</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EMPLOY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
+          <t>Lower Secondary Education</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8195,25 +8165,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B7">
-        <v>6</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IMMIGRATION</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Immigration background</t>
-        </is>
+          <t>Upper Secondary Education</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8225,25 +8190,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B8">
-        <v>7</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOT_PA_QX</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Physical activity from questionnaire data [MET-hr/day]</t>
-        </is>
+          <t>Post-secondary non-tertiary education</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8255,25 +8215,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B9">
-        <v>8</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOT_PA_AC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Physical activity from accelerometry data [MET-hr/day]</t>
-        </is>
+          <t>Short-Cycle Tertiary Education</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8285,25 +8240,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B10">
-        <v>9</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SMOKE_ST</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Smoking status</t>
-        </is>
+          <t>Bachelor's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8315,25 +8265,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B11">
-        <v>10</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOBACCO_PY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Cumulative lifetime tobacco exposure  [pack years]</t>
-        </is>
+          <t>Master's or equivalent level</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8345,25 +8290,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B12">
-        <v>11</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOBACCO_D</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Amount of daily tobacco smoked [g/day]</t>
-        </is>
+          <t>Doctoral or equivalent level</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8375,25 +8315,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B13">
-        <v>12</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EDU_LEVEL</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AGE_SMOKE_QUIT</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Age at time of quitting smoking [years]</t>
-        </is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8405,25 +8340,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B14">
-        <v>13</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MED_SUPPL</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Regular use of  vitamin/multivitamin supplements</t>
-        </is>
+          <t>employed-full time</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8435,25 +8365,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B15">
-        <v>14</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MENOPAUSE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Menopause status</t>
-        </is>
+          <t>employed-part time</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8465,25 +8390,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B16">
-        <v>15</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HRT</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hormone replacement therapy</t>
-        </is>
+          <t>housewife</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8495,25 +8415,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B17">
-        <v>16</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CONTRACEPTIVE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Use of contraceptive pills or injections [years]</t>
-        </is>
+          <t>retired</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8525,25 +8440,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B18">
-        <v>17</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LIVE_BIRTHS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Number of live births given [Nr. of birth]</t>
-        </is>
+          <t>unemployed</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>5</v>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8555,25 +8465,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B19">
-        <v>18</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AGE_FIRST_BIRTH</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Age at the first given birth [years]</t>
-        </is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8585,25 +8490,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B20">
-        <v>19</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EMPLOY</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TG</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Triglycerides measured from blood samples [mmol/L]</t>
-        </is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>7</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8615,25 +8515,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B21">
-        <v>20</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHOL</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Total cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8645,25 +8540,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B22">
-        <v>21</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IMMIGRATION</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LDL</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LDL cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8675,25 +8565,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B23">
-        <v>22</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HDL</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HDL cholesterol measured from blood samples [mmol/L]</t>
-        </is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8705,25 +8590,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B24">
-        <v>23</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PREV_DIAB</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>History of diabetes</t>
-        </is>
+          <t>former</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>2</v>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8735,25 +8615,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B25">
-        <v>24</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PREV_HYP</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>History of hypertension</t>
-        </is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8765,25 +8640,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B26">
-        <v>25</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SMOKE_ST</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PREV_CVD</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>History of cardiovascular disease</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8795,25 +8665,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B27">
-        <v>26</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PREV_CANCER</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>History of cancer</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8825,25 +8690,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B28">
-        <v>27</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MED_SUPPL</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FAM1_CHD_STROKE</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>First degree family history of premature CHD and stroke</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8855,25 +8715,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B29">
-        <v>28</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FAM1_DIAB2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>First degree family history of T2D</t>
-        </is>
+          <t>premenopausal</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8885,25 +8740,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B30">
-        <v>29</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FAM1_CANCER</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>First degree family history of cancer</t>
-        </is>
+          <t>postmenopausal</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8915,25 +8765,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B31">
-        <v>30</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DRE_SCREEN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Screening, DRE</t>
-        </is>
+          <t>perimenopausal</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8945,25 +8790,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B32">
-        <v>31</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MENOPAUSE</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PSA_SCREEN</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Screening, PSA</t>
-        </is>
+          <t>surgical postmenopausal (bilateral ovariectomy)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>3</v>
       </c>
       <c r="E32" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8975,25 +8815,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B33">
-        <v>32</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FOBT_SCREEN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Screening, FOBT</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9005,25 +8840,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B34">
-        <v>33</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HRT</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COL_SCREEN</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Screening, colonoscopy</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9035,25 +8865,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B35">
-        <v>34</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MELANOMA_SCREEN</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Screening, skin cancer</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9065,25 +8890,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B36">
-        <v>35</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PREV_DIAB</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MAMMO_SCREEN</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Screening, mammography</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9095,25 +8915,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B37">
-        <v>36</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVICAL_SCREEN</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Screening cervical, smear test</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9125,25 +8940,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B38">
-        <v>37</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PREV_HYP</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MED_STAT</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Regular use of statins</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9155,25 +8965,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B39">
-        <v>38</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MED_NSAID</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Regular use of non-steroidal anti-inflammatory drugs</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9185,25 +8990,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B40">
-        <v>39</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PREV_CVD</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INC_CVD</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CVD event during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9215,25 +9015,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B41">
-        <v>40</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AGE_CVD</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of CVD [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9245,25 +9040,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B42">
-        <v>41</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PREV_CANCER</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INC_ANGINA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Angina pectoris event during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9275,25 +9065,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B43">
-        <v>42</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AGE_ANGINA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of angina pectoris [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9305,25 +9090,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B44">
-        <v>43</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INC_MI</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Myocardial infarction during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9335,25 +9115,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B45">
-        <v>44</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FAM1_CHD_STROKE</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AGE_MI</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of myocardial infarction [years]</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>2</v>
       </c>
       <c r="E45" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9365,25 +9140,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B46">
-        <v>45</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INC_STR</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Stroke during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9395,25 +9165,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B47">
-        <v>46</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AGE_STR</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of stroke [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9425,25 +9190,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B48">
-        <v>47</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FAM1_DIAB2</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INC_ISC_STR</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Cerebral infarction (ischaemic stroke) during follow-up</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9455,25 +9215,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B49">
-        <v>48</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AGE_ISC_STR</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of cerebral infarction (ischaemic stroke) [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9485,25 +9240,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B50">
-        <v>49</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INC_HAEMO_STR</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Haemorrhagic stroke during follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9515,25 +9265,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B51">
-        <v>50</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FAM1_CANCER</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AGE_HAEMO_STR</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of haemorrhagic stroke [years]</t>
-        </is>
+          <t>I don't know</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9545,25 +9290,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B52">
-        <v>51</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INC_HYP</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Essential hypertension during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9575,25 +9315,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B53">
-        <v>52</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DRE_SCREEN</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AGE_HYP</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of essential hypertension [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9605,25 +9340,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B54">
-        <v>53</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INC_HF</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Heart failure during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9635,25 +9365,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B55">
-        <v>54</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PSA_SCREEN</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AGE_HF</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of heart failure [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9665,25 +9390,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B56">
-        <v>55</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INC_DIAB2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Diabetes mellitus type 2 during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9695,25 +9415,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B57">
-        <v>56</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FOBT_SCREEN</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AGE_DIAB2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of diabetes mellitus type 2 [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9725,25 +9440,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B58">
-        <v>57</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INC_CANCER</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Cancer during follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9755,25 +9465,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B59">
-        <v>58</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COL_SCREEN</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TYPE_CANCER</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Type of Cancer (ICD 10, 3 digits,e.g. C18.3)</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9785,25 +9490,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B60">
-        <v>59</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AGE_CANCER</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Age at diagnosis of cancer [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9815,25 +9515,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B61">
-        <v>60</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MELANOMA_SCREEN</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VITAL_ST</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Vital status at the end of mortality follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>1</v>
       </c>
       <c r="E61" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9845,25 +9540,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B62">
-        <v>61</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AGE_DEATH</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Age at time of death [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9875,25 +9565,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B63">
-        <v>62</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MAMMO_SCREEN</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VITAL_ST_CVD</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Vital status at the end of CVD mortality follow-up</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9905,25 +9590,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B64">
-        <v>63</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VITAL_ST_CANCER</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Vital status at the end of cancer mortality follow-up</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>0</v>
       </c>
       <c r="E64" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9935,25 +9615,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B65">
-        <v>64</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CERVICAL_SCREEN</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGE_FUP</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Age at end of follow-up [years]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9965,25 +9640,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B66">
-        <v>65</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BMI</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Body Mass Index at baseline [kg/m²]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>0</v>
       </c>
       <c r="E66" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -9995,25 +9665,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B67">
-        <v>66</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MED_STAT</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BMI_FUP</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Body Mass Index at follow-up [kg/m²]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>1</v>
       </c>
       <c r="E67" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10025,25 +9690,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B68">
-        <v>67</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BMI_SDS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Body Mass Index Standard Deviation Score at baseline (children studies)</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10055,25 +9715,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B69">
-        <v>68</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MED_NSAID</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BMI_SDS_FUP</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Body Mass Index Standard Deviation Score at follow-up (children studies)</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10085,25 +9740,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B70">
-        <v>69</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WAIST_FUP</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Waist circumference at follow-up [cm]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>0</v>
       </c>
       <c r="E70" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10115,25 +9765,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B71">
-        <v>70</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>INC_CVD</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WAIST</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Waist circumference at baseline [cm]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10145,25 +9790,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B72">
-        <v>71</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HIP</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Hip circumference at baseline [cm]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10175,25 +9815,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B73">
-        <v>72</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>INC_ANGINA</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HIP_FUP</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Hip circumference at follow-up [cm]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10205,25 +9840,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B74">
-        <v>73</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FMI_FUP</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Fat mass index at follow-up  [kg/m²]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>0</v>
       </c>
       <c r="E74" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10235,25 +9865,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B75">
-        <v>74</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INC_MI</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FMI</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Fat mass index at baseline  [kg/m²]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10265,25 +9890,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B76">
-        <v>75</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BODY_FAT_FUP</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Body fat precent at follow-up [%]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10295,25 +9915,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B77">
-        <v>76</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>INC_STR</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BODY_FAT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Body fat precent at baseline  [%]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10325,25 +9940,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B78">
-        <v>77</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AGE_ANTH_FUP</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Age at anthropometric measurement at follow-up [years]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10355,25 +9965,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B79">
-        <v>78</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>INC_ISC_STR</t>
+        </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ENERGY</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Energy intake [kcal/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D79">
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10385,25 +9990,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B80">
-        <v>79</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CARB</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Carbohydrate intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D80">
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10415,25 +10015,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B81">
-        <v>80</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INC_HAEMO_STR</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PROT</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Protein intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10445,25 +10040,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B82">
-        <v>81</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FAT</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Fat intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10475,25 +10065,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B83">
-        <v>82</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>INC_HYP</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALC</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Alcohol intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10505,25 +10090,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B84">
-        <v>83</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FIBER</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Dietary fiber intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10535,25 +10115,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B85">
-        <v>84</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>INC_HF</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SFA</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Saturated fat intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10565,25 +10140,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B86">
-        <v>85</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MUFA</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Monounsaturated fat intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>0</v>
       </c>
       <c r="E86" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10595,25 +10165,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B87">
-        <v>86</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>INC_DIAB2</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PUFA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Polyunsaturated fat intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10625,25 +10190,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B88">
-        <v>87</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOT_SUGARS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Total sugar intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>0</v>
       </c>
       <c r="E88" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10655,25 +10215,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B89">
-        <v>88</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>INC_CANCER</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ADD_SUGARS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Added sugar intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10685,25 +10240,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B90">
-        <v>89</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FREE_SUGARS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Free sugar intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10715,25 +10265,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B91">
-        <v>90</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VITAL_ST</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GLUC</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Glucose intake [g/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10745,25 +10290,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B92">
-        <v>91</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FRUC</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Fructose intake [g/d]</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10775,25 +10315,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B93">
-        <v>92</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CVD</t>
+        </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GI</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Daily glycaemic index</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D93">
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10805,25 +10340,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B94">
-        <v>93</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Daily glycaemic load</t>
-        </is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>0</v>
       </c>
       <c r="E94" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10835,25 +10365,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B95">
-        <v>94</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VITAL_ST_CANCER</t>
+        </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SODIUM</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Sodium intake [mg/d]</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10865,25 +10390,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B96">
-        <v>95</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOD_POT_RATIO</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Sodium to potassium intake ratio</t>
-        </is>
+          <t>FPQ (Food propensity questionnair without portion sizes)</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10895,25 +10415,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B97">
-        <v>96</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SUGAR_CONFECT_11</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Intake of sugar and similar, confectionery and water-based sweet desserts [g/d]</t>
-        </is>
+          <t>FFQ (Food frequency questionnaire)</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10925,25 +10440,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B98">
-        <v>97</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAKES_12</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Intake of cakes and fine bakery products [g/d]</t>
-        </is>
+          <t>24HDR (24-h dietary recall)</t>
+        </is>
+      </c>
+      <c r="D98">
+        <v>2</v>
       </c>
       <c r="E98" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10955,25 +10465,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B99">
-        <v>98</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FRUITVEG_JUICE_1301</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Intake of fruit and vegetable juices [g/d]</t>
-        </is>
+          <t>3_d_FR_w (3-day weighing food record)</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>3</v>
       </c>
       <c r="E99" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10985,25 +10490,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B100">
-        <v>99</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOFTDRINKS_1302</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Intake of soft drinks [g/d]</t>
-        </is>
+          <t>7_d_FR (7-day  food record; described portion sizes)</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>4</v>
       </c>
       <c r="E100" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11015,25 +10515,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B101">
-        <v>100</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ART_SWEETENER_170201</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Intake of artificial sweeteners (e.g., aspartam, saccharine) [g/d]</t>
-        </is>
+          <t>7_d_FR_w (7-day weighing food record)</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>5</v>
       </c>
       <c r="E101" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -11045,235 +10540,20 @@
           <t>KARMEN_P2</t>
         </is>
       </c>
-      <c r="B102">
-        <v>101</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DIETARY_ASSESS_INSTR</t>
+        </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VEGETABLES_02</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Vegetable intake [g/d]</t>
-        </is>
+          <t>24HFL_FFQ (24-h short food list combined with FFQ)</t>
+        </is>
+      </c>
+      <c r="D102">
+        <v>6</v>
       </c>
       <c r="E102" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B103">
-        <v>102</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>LEGUMES_TOT_03</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Total legumes intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B104">
-        <v>103</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>FRUITS_TOT_04</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Total fruit intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B105">
-        <v>104</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>RED_MEAT_0701</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Intake of red meat (mammals meat) [g/d]</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B106">
-        <v>105</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>PROCMEAT_0704</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Intake of processed or preserved meat [g/d]</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B107">
-        <v>106</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>COFFEE_130301</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Coffee intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B108">
-        <v>107</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>TEA_130302</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Tea intake [g/d]</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>KARMEN_P2</t>
-        </is>
-      </c>
-      <c r="B109">
-        <v>108</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>DIETARY_ASSESS_INSTR</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Dietary Assessment Instrument</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
         <is>
           <t>0</t>
         </is>
